--- a/output/pdf_financials_xlsx/LIBR.xlsx
+++ b/output/pdf_financials_xlsx/LIBR.xlsx
@@ -678,10 +678,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.017526</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.024158</v>
       </c>
     </row>
     <row r="13">
@@ -1032,10 +1032,10 @@
         <v>-0.613741</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.461579</v>
+        <v>-0.479105</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.171812</v>
+        <v>0.147654</v>
       </c>
     </row>
     <row r="28">
@@ -1076,10 +1076,10 @@
         <v>-0.613741</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.422664</v>
+        <v>-0.44019</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.209378</v>
+        <v>0.18522</v>
       </c>
     </row>
     <row r="30">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">

--- a/output/pdf_financials_xlsx/LIBR.xlsx
+++ b/output/pdf_financials_xlsx/LIBR.xlsx
@@ -2766,7 +2766,7 @@
         <v>-0.613741</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-0.207098</v>
+        <v>-0.461579</v>
       </c>
       <c r="F99" s="3" t="n">
         <v>0.171812</v>
@@ -2815,13 +2815,13 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003423</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>-0.031726</v>
+        <v>0.054337</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.028683</v>
+        <v>0.051718</v>
       </c>
     </row>
     <row r="102">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.07642400000000001</v>
+        <v>-0.079847</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.009476999999999999</v>
+        <v>0.076586</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.05331</v>
+        <v>0.076345</v>
       </c>
     </row>
     <row r="107">
@@ -5369,7 +5369,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -5941,7 +5945,11 @@
           <t>GST/HST receivable</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -7062,7 +7070,11 @@
           <t>GST/HST receivable</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
